--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0db672fc61af46f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcdbe2809aab0450b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reba642d22d3f40ef"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ff5499a78ef4d38"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca48685665b74e12"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36d4246970c64ba6"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcdbe2809aab0450b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc736bd7c5a5d41c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ff5499a78ef4d38"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6973da0c6d3a4752"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36d4246970c64ba6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08760ad9dde44f83"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc736bd7c5a5d41c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72f7ac2156824877"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6973da0c6d3a4752"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra724c2c121644c05"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08760ad9dde44f83"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1252f7fc322f4bc2"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72f7ac2156824877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re20132b2e8bc4061"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra724c2c121644c05"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8701389fe65b4745"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1252f7fc322f4bc2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bf632eb006e4480"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re20132b2e8bc4061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1aad3179c5364c8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8701389fe65b4745"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f879117b5474116"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bf632eb006e4480"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfad9ccea05bb4f00"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1aad3179c5364c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc326234b69b4352"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f879117b5474116"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Red5360cc5be94b14"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfad9ccea05bb4f00"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd44fa732e0f84fb2"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc326234b69b4352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd03dc217a39a4f1e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Red5360cc5be94b14"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R203a93c269a04090"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd44fa732e0f84fb2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree56e59c73204c8d"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd03dc217a39a4f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f77a86d865c4321"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R203a93c269a04090"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb45e4d0639f74e9a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree56e59c73204c8d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R943fa501b13d4aca"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f77a86d865c4321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87adae5ab6c24fd2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb45e4d0639f74e9a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R183b1ca0bd264267"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R943fa501b13d4aca"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb06df6319f240a7"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87adae5ab6c24fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31e803339ef34659"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R183b1ca0bd264267"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99796ad63fd5413d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb06df6319f240a7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87848f2a791649cb"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31e803339ef34659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reaf450b8ff4d4304"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99796ad63fd5413d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcbdb6512a12c479a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87848f2a791649cb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86545b1d9be7434b"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reaf450b8ff4d4304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc635f862eb894a10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcbdb6512a12c479a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ab745aec4b74ee3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86545b1d9be7434b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72b39c1c80964a10"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc635f862eb894a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27312096cb274e7f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ab745aec4b74ee3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9a9bf0d82504402d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72b39c1c80964a10"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f6026d23b1548fa"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27312096cb274e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62c662be9d504e45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9a9bf0d82504402d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8d8ac2496de4f2b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f6026d23b1548fa"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf80ae817d22140f7"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62c662be9d504e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R913a45551fa74769"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8d8ac2496de4f2b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raea6113f640e4de1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf80ae817d22140f7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42c7095450a4433f"/>
 </x:worksheet>
 </file>